--- a/AAII_Financials/Quarterly/TDTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TDTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
   <si>
     <t>TDTH</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,147 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="E8" s="3">
+        <v>200</v>
+      </c>
+      <c r="F8" s="3">
         <v>500</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1300</v>
       </c>
       <c r="G8" s="3">
         <v>500</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+      <c r="H8" s="3">
+        <v>200</v>
+      </c>
+      <c r="I8" s="3">
+        <v>200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>400</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="E9" s="3">
+        <v>200</v>
+      </c>
+      <c r="F9" s="3">
         <v>400</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1000</v>
       </c>
       <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="H9" s="3">
+        <v>200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>200</v>
+      </c>
+      <c r="J9" s="3">
+        <v>300</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>300</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -808,37 +834,45 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E12" s="3">
+        <v>100</v>
+      </c>
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
-        <v>300</v>
-      </c>
       <c r="G12" s="3">
+        <v>200</v>
+      </c>
+      <c r="H12" s="3">
         <v>100</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="I12" s="3">
+        <v>100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>100</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -866,37 +900,49 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -924,8 +970,14 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -934,66 +986,80 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>1200</v>
       </c>
       <c r="E17" s="3">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F17" s="3">
-        <v>2500</v>
+        <v>1900</v>
       </c>
       <c r="G17" s="3">
-        <v>700</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>1900</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J17" s="3">
+        <v>900</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-1000</v>
       </c>
       <c r="E18" s="3">
-        <v>-1900</v>
+        <v>-1000</v>
       </c>
       <c r="F18" s="3">
-        <v>-1200</v>
+        <v>-1400</v>
       </c>
       <c r="G18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>-1400</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-500</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1005,66 +1071,80 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-900</v>
       </c>
       <c r="E21" s="3">
-        <v>-1800</v>
+        <v>-900</v>
       </c>
       <c r="F21" s="3">
-        <v>-1100</v>
+        <v>-1400</v>
       </c>
       <c r="G21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-1400</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1080,11 +1160,11 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1092,51 +1172,63 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>-1000</v>
       </c>
       <c r="E23" s="3">
-        <v>-1900</v>
+        <v>-1000</v>
       </c>
       <c r="F23" s="3">
-        <v>-1100</v>
+        <v>-1500</v>
       </c>
       <c r="G23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>-1500</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-500</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1144,14 +1236,20 @@
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1179,66 +1277,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-1000</v>
       </c>
       <c r="E26" s="3">
-        <v>-1900</v>
+        <v>-1000</v>
       </c>
       <c r="F26" s="3">
-        <v>-1100</v>
+        <v>-1500</v>
       </c>
       <c r="G26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>-1500</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-500</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-1000</v>
       </c>
       <c r="E27" s="3">
-        <v>-1900</v>
+        <v>-1000</v>
       </c>
       <c r="F27" s="3">
-        <v>-1100</v>
+        <v>-1500</v>
       </c>
       <c r="G27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>-1500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-500</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1266,8 +1382,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1295,8 +1417,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1324,8 +1452,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1353,66 +1487,84 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-1000</v>
       </c>
       <c r="E33" s="3">
-        <v>-1900</v>
+        <v>-1000</v>
       </c>
       <c r="F33" s="3">
-        <v>-1100</v>
+        <v>-1500</v>
       </c>
       <c r="G33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>-1500</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-500</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1440,71 +1592,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-1000</v>
       </c>
       <c r="E35" s="3">
-        <v>-1900</v>
+        <v>-1000</v>
       </c>
       <c r="F35" s="3">
-        <v>-1100</v>
+        <v>-1500</v>
       </c>
       <c r="G35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>-1500</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-500</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1516,8 +1686,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1529,240 +1701,290 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>1800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H41" s="3">
         <v>4000</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+      <c r="I41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J41" s="3">
+        <v>900</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>100</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="G42" s="3">
+        <v>100</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>100</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>1700</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="F43" s="3">
+        <v>100</v>
+      </c>
+      <c r="G43" s="3">
+        <v>100</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>100</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>500</v>
+        <v>2200</v>
       </c>
       <c r="E45" s="3">
-        <v>400</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>2200</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>300</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F46" s="3">
         <v>4000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H46" s="3">
         <v>6200</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+      <c r="I46" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1400</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>200</v>
+        <v>1300</v>
       </c>
       <c r="E48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H48" s="3">
         <v>1700</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+      <c r="I48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1600</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1790,8 +2012,14 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1819,8 +2047,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1848,37 +2082,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1906,37 +2152,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F54" s="3">
         <v>5800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H54" s="3">
         <v>7900</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+      <c r="I54" s="3">
+        <v>7900</v>
+      </c>
+      <c r="J54" s="3">
+        <v>3000</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1948,8 +2206,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1961,161 +2221,193 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="F57" s="3">
+        <v>200</v>
+      </c>
+      <c r="G57" s="3">
+        <v>200</v>
+      </c>
+      <c r="H57" s="3">
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
+        <v>100</v>
+      </c>
+      <c r="J57" s="3">
+        <v>200</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>1000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>500</v>
+      </c>
+      <c r="G58" s="3">
+        <v>500</v>
+      </c>
+      <c r="H58" s="3">
+        <v>500</v>
+      </c>
+      <c r="I58" s="3">
+        <v>500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>900</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H59" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I59" s="3">
+        <v>8600</v>
+      </c>
+      <c r="J59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
-        <v>9300</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F60" s="3">
         <v>2000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H60" s="3">
         <v>9500</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+      <c r="I60" s="3">
+        <v>9500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>2600</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="E61" s="3">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>700</v>
       </c>
       <c r="E62" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2135,8 +2427,14 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2164,8 +2462,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2193,8 +2497,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2222,37 +2532,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F66" s="3">
         <v>3400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H66" s="3">
         <v>11100</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+      <c r="I66" s="3">
+        <v>11100</v>
+      </c>
+      <c r="J66" s="3">
+        <v>4300</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2264,8 +2586,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2293,8 +2617,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2322,8 +2652,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2351,8 +2687,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2380,37 +2722,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-6200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="H72" s="3">
         <v>-3300</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+      <c r="I72" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-1300</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2438,8 +2792,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2467,8 +2827,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2496,37 +2862,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
+      <c r="D76" s="3">
+        <v>500</v>
       </c>
       <c r="E76" s="3">
+        <v>500</v>
+      </c>
+      <c r="F76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H76" s="3">
         <v>-3200</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+      <c r="I76" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="J76" s="3">
+        <v>-1300</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2554,71 +2932,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-1000</v>
       </c>
       <c r="E81" s="3">
-        <v>-1900</v>
+        <v>-1000</v>
       </c>
       <c r="F81" s="3">
-        <v>-1100</v>
+        <v>-1500</v>
       </c>
       <c r="G81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>-1500</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-500</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2630,28 +3026,30 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -2659,8 +3057,14 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2688,8 +3092,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2717,8 +3127,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2746,8 +3162,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2775,8 +3197,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2804,37 +3232,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E89" s="3">
-        <v>-2400</v>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F89" s="3">
-        <v>-600</v>
+        <v>-1300</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>-1300</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-300</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2846,19 +3286,21 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -2875,8 +3317,14 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2904,8 +3352,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2933,37 +3387,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-100</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2975,22 +3441,24 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -2999,13 +3467,19 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3033,8 +3507,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3062,8 +3542,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3091,37 +3577,49 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>5900</v>
-      </c>
-      <c r="E100" s="3">
-        <v>5400</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="G100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="H100" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I100" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J100" s="3">
+        <v>700</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3129,7 +3627,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -3137,11 +3635,11 @@
       <c r="G101" s="3">
         <v>0</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -3149,33 +3647,45 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>700</v>
+        <v>-1100</v>
       </c>
       <c r="G102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>-1100</v>
+      </c>
+      <c r="H102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J102" s="3">
+        <v>400</v>
       </c>
       <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TDTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TDTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>TDTH</t>
   </si>
@@ -656,138 +656,157 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3">
         <v>200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -798,31 +817,37 @@
         <v>0</v>
       </c>
       <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
       <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,43 +861,51 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>300</v>
+      </c>
+      <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>100</v>
       </c>
       <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
+      <c r="K12" s="3">
+        <v>100</v>
+      </c>
+      <c r="L12" s="3">
+        <v>100</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,8 +939,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -932,17 +971,23 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -976,8 +1021,14 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,78 +1039,92 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F17" s="3">
         <v>1200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>900</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-500</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,8 +1138,10 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1099,52 +1166,64 @@
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1160,17 +1239,17 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1178,51 +1257,63 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1236,20 +1327,26 @@
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,78 +1380,96 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-500</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-500</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1503,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1544,14 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1585,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,8 +1626,14 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1519,52 +1658,64 @@
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-500</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,83 +1749,101 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-500</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +1857,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,78 +1874,92 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>1800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>900</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>100</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>100</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1791,25 +1976,31 @@
         <v>100</v>
       </c>
       <c r="H43" s="3">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3">
+        <v>100</v>
+      </c>
+      <c r="J43" s="3">
         <v>1100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1834,87 +2025,105 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F45" s="3">
         <v>2200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>2200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F46" s="3">
         <v>2700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>6200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1400</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1939,52 +2148,64 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F48" s="3">
         <v>1300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1600</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2018,8 +2239,14 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2280,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,16 +2321,22 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>200</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -2114,17 +2353,23 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,43 +2403,55 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F54" s="3">
         <v>4000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>7900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>7900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2465,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,57 +2482,65 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>300</v>
+      </c>
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>400</v>
+      </c>
+      <c r="F58" s="3">
         <v>1000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>500</v>
       </c>
       <c r="H58" s="3">
         <v>500</v>
@@ -2282,19 +2549,25 @@
         <v>500</v>
       </c>
       <c r="J58" s="3">
+        <v>500</v>
+      </c>
+      <c r="K58" s="3">
+        <v>500</v>
+      </c>
+      <c r="L58" s="3">
         <v>900</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2305,116 +2578,134 @@
         <v>500</v>
       </c>
       <c r="F59" s="3">
+        <v>500</v>
+      </c>
+      <c r="G59" s="3">
+        <v>500</v>
+      </c>
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>8600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>8600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1300</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F60" s="3">
         <v>1900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>9500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>9500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F61" s="3">
         <v>900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
         <v>700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2433,8 +2724,14 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +2765,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +2806,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,43 +2847,55 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F66" s="3">
         <v>3600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>11100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>11100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4300</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +2909,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +2946,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +2987,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2693,8 +3028,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,43 +3069,55 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-8100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-8100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-6200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-6200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-3300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-3300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-1300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +3151,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3192,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,43 +3233,55 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F76" s="3">
         <v>500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-3200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-3200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-1300</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,83 +3315,101 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-500</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,16 +3423,18 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
-        <v>100</v>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -3046,16 +3443,16 @@
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -3063,8 +3460,14 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3501,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3542,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3583,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +3624,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,8 +3665,14 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3249,32 +3682,38 @@
       <c r="E89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1300</v>
       </c>
-      <c r="G89" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,8 +3727,10 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3299,17 +3740,17 @@
       <c r="E91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -3323,8 +3764,14 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +3805,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,8 +3846,14 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3404,32 +3863,38 @@
       <c r="E94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,8 +3908,10 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3460,26 +3927,32 @@
       <c r="G96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>100</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +3986,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +4027,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,8 +4068,14 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3594,40 +4085,46 @@
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
-        <v>200</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>2700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>2700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -3641,11 +4138,11 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -3653,8 +4150,14 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3665,27 +4168,33 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-1100</v>
       </c>
-      <c r="G102" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>400</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TDTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TDTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>TDTH</t>
   </si>
@@ -734,11 +734,11 @@
       <c r="E8" s="3">
         <v>0</v>
       </c>
-      <c r="F8" s="3">
-        <v>200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>200</v>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
         <v>500</v>
@@ -775,11 +775,11 @@
       <c r="E9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
-        <v>200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>200</v>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="3">
         <v>400</v>
@@ -816,11 +816,11 @@
       <c r="E10" s="3">
         <v>0</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
@@ -874,11 +874,11 @@
       <c r="E12" s="3">
         <v>300</v>
       </c>
-      <c r="F12" s="3">
-        <v>100</v>
-      </c>
-      <c r="G12" s="3">
-        <v>100</v>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H12" s="3">
         <v>200</v>
@@ -1052,11 +1052,11 @@
       <c r="E17" s="3">
         <v>3100</v>
       </c>
-      <c r="F17" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1200</v>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H17" s="3">
         <v>1900</v>
@@ -1093,11 +1093,11 @@
       <c r="E18" s="3">
         <v>-3100</v>
       </c>
-      <c r="F18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1000</v>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H18" s="3">
         <v>-1400</v>
@@ -1151,11 +1151,11 @@
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1193,10 +1193,10 @@
         <v>-3000</v>
       </c>
       <c r="F21" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>-1400</v>
@@ -1233,11 +1233,11 @@
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1274,11 +1274,11 @@
       <c r="E23" s="3">
         <v>-3100</v>
       </c>
-      <c r="F23" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-1000</v>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H23" s="3">
         <v>-1500</v>
@@ -1397,11 +1397,11 @@
       <c r="E26" s="3">
         <v>-3100</v>
       </c>
-      <c r="F26" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-1000</v>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H26" s="3">
         <v>-1500</v>
@@ -1438,11 +1438,11 @@
       <c r="E27" s="3">
         <v>-3100</v>
       </c>
-      <c r="F27" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-1000</v>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H27" s="3">
         <v>-1500</v>
@@ -1643,11 +1643,11 @@
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -1684,11 +1684,11 @@
       <c r="E33" s="3">
         <v>-3100</v>
       </c>
-      <c r="F33" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-1000</v>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H33" s="3">
         <v>-1500</v>
@@ -1766,11 +1766,11 @@
       <c r="E35" s="3">
         <v>-3100</v>
       </c>
-      <c r="F35" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-1000</v>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H35" s="3">
         <v>-1500</v>
@@ -1887,11 +1887,11 @@
       <c r="E41" s="3">
         <v>200</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3">
-        <v>0</v>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H41" s="3">
         <v>1800</v>
@@ -1969,11 +1969,11 @@
       <c r="E43" s="3">
         <v>100</v>
       </c>
-      <c r="F43" s="3">
-        <v>100</v>
-      </c>
-      <c r="G43" s="3">
-        <v>100</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3">
         <v>100</v>
@@ -2051,11 +2051,11 @@
       <c r="E45" s="3">
         <v>1200</v>
       </c>
-      <c r="F45" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2200</v>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
         <v>1900</v>
@@ -2092,11 +2092,11 @@
       <c r="E46" s="3">
         <v>1700</v>
       </c>
-      <c r="F46" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G46" s="3">
-        <v>2700</v>
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3">
         <v>4000</v>
@@ -2174,11 +2174,11 @@
       <c r="E48" s="3">
         <v>1100</v>
       </c>
-      <c r="F48" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1300</v>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3">
         <v>1800</v>
@@ -2215,11 +2215,11 @@
       <c r="E49" s="3">
         <v>0</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
@@ -2420,11 +2420,11 @@
       <c r="E54" s="3">
         <v>3000</v>
       </c>
-      <c r="F54" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G54" s="3">
-        <v>4000</v>
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H54" s="3">
         <v>5800</v>
@@ -2495,11 +2495,11 @@
       <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
-        <v>100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>100</v>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3">
         <v>200</v>
@@ -2536,11 +2536,11 @@
       <c r="E58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1000</v>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3">
         <v>500</v>
@@ -2577,11 +2577,11 @@
       <c r="E59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
-        <v>500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>500</v>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3">
         <v>1000</v>
@@ -2618,11 +2618,11 @@
       <c r="E60" s="3">
         <v>1300</v>
       </c>
-      <c r="F60" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1900</v>
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3">
         <v>2000</v>
@@ -2660,10 +2660,10 @@
         <v>2000</v>
       </c>
       <c r="F61" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>1400</v>
@@ -2700,11 +2700,11 @@
       <c r="E62" s="3">
         <v>0</v>
       </c>
-      <c r="F62" s="3">
-        <v>700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>700</v>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2864,11 +2864,11 @@
       <c r="E66" s="3">
         <v>3400</v>
       </c>
-      <c r="F66" s="3">
-        <v>3600</v>
-      </c>
-      <c r="G66" s="3">
-        <v>3600</v>
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H66" s="3">
         <v>3400</v>
@@ -3086,11 +3086,11 @@
       <c r="E72" s="3">
         <v>-14300</v>
       </c>
-      <c r="F72" s="3">
-        <v>-8100</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-8100</v>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H72" s="3">
         <v>-6200</v>
@@ -3250,11 +3250,11 @@
       <c r="E76" s="3">
         <v>-400</v>
       </c>
-      <c r="F76" s="3">
-        <v>500</v>
-      </c>
-      <c r="G76" s="3">
-        <v>500</v>
+      <c r="F76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H76" s="3">
         <v>2400</v>
@@ -3378,11 +3378,11 @@
       <c r="E81" s="3">
         <v>-3100</v>
       </c>
-      <c r="F81" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-1000</v>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H81" s="3">
         <v>-1500</v>

--- a/AAII_Financials/Quarterly/TDTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TDTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>TDTH</t>
   </si>
@@ -656,56 +656,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="I7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="J7" s="2">
         <v>45291</v>
-      </c>
-      <c r="G7" s="2">
-        <v>45199</v>
-      </c>
-      <c r="H7" s="2">
-        <v>45107</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44926</v>
       </c>
       <c r="K7" s="2">
         <v>45016</v>
@@ -713,17 +717,23 @@
       <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
+      <c r="M7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="N7" s="2">
+        <v>44926</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -734,10 +744,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
         <v>200</v>
@@ -746,7 +756,7 @@
         <v>200</v>
       </c>
       <c r="J8" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K8" s="3">
         <v>200</v>
@@ -754,31 +764,37 @@
       <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
+      <c r="M8" s="3">
+        <v>200</v>
+      </c>
+      <c r="N8" s="3">
+        <v>400</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>100</v>
-      </c>
-      <c r="F9" s="3">
-        <v>400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>400</v>
       </c>
       <c r="H9" s="3">
         <v>200</v>
@@ -787,7 +803,7 @@
         <v>200</v>
       </c>
       <c r="J9" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K9" s="3">
         <v>200</v>
@@ -795,17 +811,23 @@
       <c r="L9" s="3">
         <v>300</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
+      <c r="M9" s="3">
+        <v>200</v>
+      </c>
+      <c r="N9" s="3">
+        <v>300</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -816,10 +838,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
@@ -836,17 +858,23 @@
       <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>100</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,22 +890,24 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>200</v>
+      </c>
+      <c r="F12" s="3">
         <v>300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>300</v>
-      </c>
-      <c r="F12" s="3">
-        <v>200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>200</v>
       </c>
       <c r="H12" s="3">
         <v>100</v>
@@ -886,7 +916,7 @@
         <v>100</v>
       </c>
       <c r="J12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K12" s="3">
         <v>100</v>
@@ -894,17 +924,23 @@
       <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
+      <c r="M12" s="3">
+        <v>100</v>
+      </c>
+      <c r="N12" s="3">
+        <v>100</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,8 +980,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -976,17 +1018,23 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1026,8 +1074,14 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1040,22 +1094,24 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F17" s="3">
         <v>3100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3100</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1900</v>
       </c>
       <c r="H17" s="3">
         <v>1200</v>
@@ -1064,7 +1120,7 @@
         <v>1200</v>
       </c>
       <c r="J17" s="3">
-        <v>900</v>
+        <v>1900</v>
       </c>
       <c r="K17" s="3">
         <v>1200</v>
@@ -1072,31 +1128,37 @@
       <c r="L17" s="3">
         <v>900</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
+      <c r="M17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N17" s="3">
+        <v>900</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3100</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1400</v>
       </c>
       <c r="H18" s="3">
         <v>-1000</v>
@@ -1105,7 +1167,7 @@
         <v>-1000</v>
       </c>
       <c r="J18" s="3">
-        <v>-500</v>
+        <v>-1400</v>
       </c>
       <c r="K18" s="3">
         <v>-1000</v>
@@ -1113,17 +1175,23 @@
       <c r="L18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
+      <c r="M18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-500</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1139,8 +1207,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1171,31 +1241,37 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-3000</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-1400</v>
       </c>
       <c r="H21" s="3">
         <v>-900</v>
@@ -1204,7 +1280,7 @@
         <v>-900</v>
       </c>
       <c r="J21" s="3">
-        <v>-500</v>
+        <v>-1400</v>
       </c>
       <c r="K21" s="3">
         <v>-900</v>
@@ -1212,17 +1288,23 @@
       <c r="L21" s="3">
         <v>-500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
+      <c r="M21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-500</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1238,11 +1320,11 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1253,8 +1335,8 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1262,31 +1344,37 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J23" s="3">
         <v>-1500</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-500</v>
       </c>
       <c r="K23" s="3">
         <v>-900</v>
@@ -1294,31 +1382,37 @@
       <c r="L23" s="3">
         <v>-500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
+      <c r="M23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-500</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1326,8 +1420,8 @@
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1338,14 +1432,20 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1385,31 +1485,37 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J26" s="3">
         <v>-1500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-500</v>
       </c>
       <c r="K26" s="3">
         <v>-900</v>
@@ -1417,40 +1523,46 @@
       <c r="L26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
+      <c r="M26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-500</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J27" s="3">
         <v>-1500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-500</v>
       </c>
       <c r="K27" s="3">
         <v>-900</v>
@@ -1458,17 +1570,23 @@
       <c r="L27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
+      <c r="M27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-500</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1508,8 +1626,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1549,8 +1673,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1590,8 +1720,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1631,8 +1767,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1663,40 +1805,46 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J33" s="3">
         <v>-1500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-500</v>
       </c>
       <c r="K33" s="3">
         <v>-900</v>
@@ -1704,17 +1852,23 @@
       <c r="L33" s="3">
         <v>-500</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
+      <c r="M33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-500</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1754,31 +1908,37 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J35" s="3">
         <v>-1500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-500</v>
       </c>
       <c r="K35" s="3">
         <v>-900</v>
@@ -1786,45 +1946,51 @@
       <c r="L35" s="3">
         <v>-500</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
+      <c r="M35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-500</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="I38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="J38" s="2">
         <v>45291</v>
-      </c>
-      <c r="G38" s="2">
-        <v>45199</v>
-      </c>
-      <c r="H38" s="2">
-        <v>45107</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44926</v>
       </c>
       <c r="K38" s="2">
         <v>45016</v>
@@ -1832,17 +1998,23 @@
       <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
+      <c r="M38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="N38" s="2">
+        <v>44926</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1858,8 +2030,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1875,8 +2049,10 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1887,19 +2063,19 @@
         <v>200</v>
       </c>
       <c r="F41" s="3">
+        <v>200</v>
+      </c>
+      <c r="G41" s="3">
+        <v>200</v>
+      </c>
+      <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
         <v>1800</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H41" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I41" s="3">
-        <v>4000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>900</v>
       </c>
       <c r="K41" s="3">
         <v>4000</v>
@@ -1907,17 +2083,23 @@
       <c r="L41" s="3">
         <v>900</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
+      <c r="M41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="N41" s="3">
+        <v>900</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1948,17 +2130,23 @@
       <c r="L42" s="3">
         <v>100</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>100</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1975,10 +2163,10 @@
         <v>100</v>
       </c>
       <c r="H43" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="I43" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
@@ -1989,17 +2177,23 @@
       <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
+      <c r="M43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N43" s="3">
+        <v>100</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2030,17 +2224,23 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2051,19 +2251,19 @@
         <v>1200</v>
       </c>
       <c r="F45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J45" s="3">
         <v>1900</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>300</v>
       </c>
       <c r="K45" s="3">
         <v>1000</v>
@@ -2071,17 +2271,23 @@
       <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
+      <c r="M45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N45" s="3">
+        <v>300</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2092,19 +2298,19 @@
         <v>1700</v>
       </c>
       <c r="F46" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G46" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H46" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I46" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J46" s="3">
         <v>4000</v>
-      </c>
-      <c r="G46" s="3">
-        <v>4000</v>
-      </c>
-      <c r="H46" s="3">
-        <v>6200</v>
-      </c>
-      <c r="I46" s="3">
-        <v>6200</v>
-      </c>
-      <c r="J46" s="3">
-        <v>1400</v>
       </c>
       <c r="K46" s="3">
         <v>6200</v>
@@ -2112,17 +2318,23 @@
       <c r="L46" s="3">
         <v>1400</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
+      <c r="M46" s="3">
+        <v>6200</v>
+      </c>
+      <c r="N46" s="3">
+        <v>1400</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2153,40 +2365,46 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J48" s="3">
         <v>1800</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1600</v>
       </c>
       <c r="K48" s="3">
         <v>1700</v>
@@ -2194,17 +2412,23 @@
       <c r="L48" s="3">
         <v>1600</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
+      <c r="M48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N48" s="3">
+        <v>1600</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2244,8 +2468,14 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2285,8 +2515,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2326,23 +2562,29 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3">
         <v>200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2358,17 +2600,23 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2408,31 +2656,37 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F54" s="3">
         <v>3000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>3000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I54" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J54" s="3">
         <v>5800</v>
-      </c>
-      <c r="G54" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H54" s="3">
-        <v>7900</v>
-      </c>
-      <c r="I54" s="3">
-        <v>7900</v>
-      </c>
-      <c r="J54" s="3">
-        <v>3000</v>
       </c>
       <c r="K54" s="3">
         <v>7900</v>
@@ -2440,17 +2694,23 @@
       <c r="L54" s="3">
         <v>3000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
+      <c r="M54" s="3">
+        <v>7900</v>
+      </c>
+      <c r="N54" s="3">
+        <v>3000</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2466,8 +2726,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2483,8 +2745,10 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2495,10 +2759,10 @@
         <v>300</v>
       </c>
       <c r="F57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
@@ -2515,40 +2779,46 @@
       <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
+      <c r="M57" s="3">
+        <v>100</v>
+      </c>
+      <c r="N57" s="3">
+        <v>200</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>500</v>
+      </c>
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J58" s="3">
         <v>500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>500</v>
-      </c>
-      <c r="H58" s="3">
-        <v>500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>500</v>
-      </c>
-      <c r="J58" s="3">
-        <v>900</v>
       </c>
       <c r="K58" s="3">
         <v>500</v>
@@ -2556,40 +2826,46 @@
       <c r="L58" s="3">
         <v>900</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>500</v>
+      </c>
+      <c r="N58" s="3">
+        <v>900</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>700</v>
+      </c>
+      <c r="F59" s="3">
         <v>500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
+        <v>500</v>
+      </c>
+      <c r="I59" s="3">
+        <v>500</v>
+      </c>
+      <c r="J59" s="3">
         <v>1000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>8600</v>
-      </c>
-      <c r="I59" s="3">
-        <v>8600</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1300</v>
       </c>
       <c r="K59" s="3">
         <v>8600</v>
@@ -2597,40 +2873,46 @@
       <c r="L59" s="3">
         <v>1300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
+      <c r="M59" s="3">
+        <v>8600</v>
+      </c>
+      <c r="N59" s="3">
+        <v>1300</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F60" s="3">
         <v>1300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J60" s="3">
         <v>2000</v>
-      </c>
-      <c r="G60" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H60" s="3">
-        <v>9500</v>
-      </c>
-      <c r="I60" s="3">
-        <v>9500</v>
-      </c>
-      <c r="J60" s="3">
-        <v>2600</v>
       </c>
       <c r="K60" s="3">
         <v>9500</v>
@@ -2638,40 +2920,46 @@
       <c r="L60" s="3">
         <v>2600</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
+      <c r="M60" s="3">
+        <v>9500</v>
+      </c>
+      <c r="N60" s="3">
+        <v>2600</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F61" s="3">
         <v>2000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
+        <v>900</v>
+      </c>
+      <c r="I61" s="3">
+        <v>900</v>
+      </c>
+      <c r="J61" s="3">
         <v>1400</v>
-      </c>
-      <c r="G61" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H61" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I61" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J61" s="3">
-        <v>1700</v>
       </c>
       <c r="K61" s="3">
         <v>1600</v>
@@ -2680,36 +2968,42 @@
         <v>1700</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>700</v>
+      </c>
+      <c r="I62" s="3">
+        <v>700</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -2729,8 +3023,14 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2770,8 +3070,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2811,8 +3117,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2852,16 +3164,22 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3400</v>
+        <v>8000</v>
       </c>
       <c r="E66" s="3">
-        <v>3400</v>
+        <v>8000</v>
       </c>
       <c r="F66" s="3">
         <v>3400</v>
@@ -2870,13 +3188,13 @@
         <v>3400</v>
       </c>
       <c r="H66" s="3">
-        <v>11100</v>
+        <v>3600</v>
       </c>
       <c r="I66" s="3">
-        <v>11100</v>
+        <v>3600</v>
       </c>
       <c r="J66" s="3">
-        <v>4300</v>
+        <v>3400</v>
       </c>
       <c r="K66" s="3">
         <v>11100</v>
@@ -2884,17 +3202,23 @@
       <c r="L66" s="3">
         <v>4300</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
+      <c r="M66" s="3">
+        <v>11100</v>
+      </c>
+      <c r="N66" s="3">
+        <v>4300</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2910,8 +3234,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2951,8 +3277,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2992,8 +3324,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3033,8 +3371,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3074,31 +3418,37 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-14300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-14300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="J72" s="3">
         <v>-6200</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-1300</v>
       </c>
       <c r="K72" s="3">
         <v>-3300</v>
@@ -3106,17 +3456,23 @@
       <c r="L72" s="3">
         <v>-1300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
+      <c r="M72" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="N72" s="3">
+        <v>-1300</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3156,8 +3512,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3197,8 +3559,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3238,31 +3606,37 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F76" s="3">
         <v>-400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
+        <v>500</v>
+      </c>
+      <c r="I76" s="3">
+        <v>500</v>
+      </c>
+      <c r="J76" s="3">
         <v>2400</v>
-      </c>
-      <c r="G76" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H76" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-1300</v>
       </c>
       <c r="K76" s="3">
         <v>-3200</v>
@@ -3270,17 +3644,23 @@
       <c r="L76" s="3">
         <v>-1300</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
+      <c r="M76" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="N76" s="3">
+        <v>-1300</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3320,36 +3700,42 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="I80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="J80" s="2">
         <v>45291</v>
-      </c>
-      <c r="G80" s="2">
-        <v>45199</v>
-      </c>
-      <c r="H80" s="2">
-        <v>45107</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44926</v>
       </c>
       <c r="K80" s="2">
         <v>45016</v>
@@ -3357,40 +3743,46 @@
       <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
+      <c r="M80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="N80" s="2">
+        <v>44926</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J81" s="3">
         <v>-1500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-500</v>
       </c>
       <c r="K81" s="3">
         <v>-900</v>
@@ -3398,17 +3790,23 @@
       <c r="L81" s="3">
         <v>-500</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
+      <c r="M81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-500</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3424,31 +3822,33 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3456,8 +3856,8 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -3465,8 +3865,14 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3506,8 +3912,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3547,8 +3959,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3588,8 +4006,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3629,8 +4053,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3670,31 +4100,37 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="D89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1300</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-300</v>
       </c>
       <c r="K89" s="3">
         <v>-1200</v>
@@ -3702,17 +4138,23 @@
       <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="M89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-300</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3728,19 +4170,21 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>3</v>
@@ -3769,8 +4213,14 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3810,8 +4260,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3851,19 +4307,25 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -3883,17 +4345,23 @@
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3909,8 +4377,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3926,14 +4396,14 @@
       <c r="G96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>100</v>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3945,13 +4415,19 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3991,8 +4467,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4032,8 +4514,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4073,31 +4561,37 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="D100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
+        <v>300</v>
+      </c>
+      <c r="I100" s="3">
+        <v>300</v>
+      </c>
+      <c r="J100" s="3">
         <v>200</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I100" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J100" s="3">
-        <v>700</v>
       </c>
       <c r="K100" s="3">
         <v>2700</v>
@@ -4105,17 +4599,23 @@
       <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="M100" s="3">
+        <v>2700</v>
+      </c>
+      <c r="N100" s="3">
+        <v>700</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4128,8 +4628,8 @@
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
@@ -4137,8 +4637,8 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4146,8 +4646,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -4155,8 +4655,14 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4167,19 +4673,19 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1100</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I102" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J102" s="3">
-        <v>400</v>
       </c>
       <c r="K102" s="3">
         <v>1500</v>
@@ -4187,13 +4693,19 @@
       <c r="L102" s="3">
         <v>400</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N102" s="3">
+        <v>400</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TDTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TDTH_QTR_FIN.xlsx
@@ -656,66 +656,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
-      </c>
-      <c r="K7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="L7" s="2">
-        <v>44926</v>
       </c>
       <c r="M7" s="2">
         <v>45016</v>
@@ -723,17 +724,23 @@
       <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
+      <c r="O7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="P7" s="2">
+        <v>44926</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -741,7 +748,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
@@ -750,19 +757,19 @@
         <v>0</v>
       </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>200</v>
-      </c>
-      <c r="I8" s="3">
-        <v>200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>500</v>
       </c>
       <c r="K8" s="3">
         <v>200</v>
       </c>
       <c r="L8" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M8" s="3">
         <v>200</v>
@@ -770,17 +777,23 @@
       <c r="N8" s="3">
         <v>400</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
+      <c r="O8" s="3">
+        <v>200</v>
+      </c>
+      <c r="P8" s="3">
+        <v>400</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -791,25 +804,25 @@
         <v>0</v>
       </c>
       <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>400</v>
       </c>
       <c r="K9" s="3">
         <v>200</v>
       </c>
       <c r="L9" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M9" s="3">
         <v>200</v>
@@ -817,17 +830,23 @@
       <c r="N9" s="3">
         <v>300</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
+      <c r="O9" s="3">
+        <v>200</v>
+      </c>
+      <c r="P9" s="3">
+        <v>300</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -864,17 +883,23 @@
       <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>100</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,37 +917,39 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>400</v>
+      </c>
+      <c r="E12" s="3">
+        <v>400</v>
+      </c>
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>100</v>
-      </c>
-      <c r="J12" s="3">
-        <v>200</v>
       </c>
       <c r="K12" s="3">
         <v>100</v>
       </c>
       <c r="L12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M12" s="3">
         <v>100</v>
@@ -930,17 +957,23 @@
       <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
+      <c r="O12" s="3">
+        <v>100</v>
+      </c>
+      <c r="P12" s="3">
+        <v>100</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,16 +1019,22 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1900</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1024,17 +1063,23 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1125,14 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,37 +1147,39 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F17" s="3">
         <v>5700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1200</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1900</v>
       </c>
       <c r="K17" s="3">
         <v>1200</v>
       </c>
       <c r="L17" s="3">
-        <v>900</v>
+        <v>1900</v>
       </c>
       <c r="M17" s="3">
         <v>1200</v>
@@ -1134,46 +1187,52 @@
       <c r="N17" s="3">
         <v>900</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
+      <c r="O17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P17" s="3">
+        <v>900</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-5700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-5700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1400</v>
       </c>
       <c r="K18" s="3">
         <v>-1000</v>
       </c>
       <c r="L18" s="3">
-        <v>-500</v>
+        <v>-1400</v>
       </c>
       <c r="M18" s="3">
         <v>-1000</v>
@@ -1181,17 +1240,23 @@
       <c r="N18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
+      <c r="O18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-500</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,16 +1274,18 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1247,46 +1314,52 @@
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-5600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-5600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-3000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-3000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-900</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-1400</v>
       </c>
       <c r="K21" s="3">
         <v>-900</v>
       </c>
       <c r="L21" s="3">
-        <v>-500</v>
+        <v>-1400</v>
       </c>
       <c r="M21" s="3">
         <v>-900</v>
@@ -1294,25 +1367,31 @@
       <c r="N21" s="3">
         <v>-500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
+      <c r="O21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-500</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1329,8 +1408,8 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1341,8 +1420,8 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1350,37 +1429,43 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-5600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-3100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-900</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-500</v>
       </c>
       <c r="M23" s="3">
         <v>-900</v>
@@ -1388,37 +1473,43 @@
       <c r="N23" s="3">
         <v>-500</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
+      <c r="O23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-500</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1426,8 +1517,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
@@ -1438,14 +1529,20 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,37 +1588,43 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-5600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-5600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-500</v>
       </c>
       <c r="M26" s="3">
         <v>-900</v>
@@ -1529,46 +1632,52 @@
       <c r="N26" s="3">
         <v>-500</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
+      <c r="O26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-500</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-500</v>
       </c>
       <c r="M27" s="3">
         <v>-900</v>
@@ -1576,17 +1685,23 @@
       <c r="N27" s="3">
         <v>-500</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
+      <c r="O27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-500</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1747,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1800,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1853,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,16 +1906,22 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -1811,46 +1950,52 @@
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-500</v>
       </c>
       <c r="M33" s="3">
         <v>-900</v>
@@ -1858,17 +2003,23 @@
       <c r="N33" s="3">
         <v>-500</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
+      <c r="O33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-500</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,37 +2065,43 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-500</v>
       </c>
       <c r="M35" s="3">
         <v>-900</v>
@@ -1952,51 +2109,57 @@
       <c r="N35" s="3">
         <v>-500</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
+      <c r="O35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-500</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
-      </c>
-      <c r="K38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="L38" s="2">
-        <v>44926</v>
       </c>
       <c r="M38" s="2">
         <v>45016</v>
@@ -2004,17 +2167,23 @@
       <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
+      <c r="O38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="P38" s="2">
+        <v>44926</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2201,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,8 +2222,10 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2069,19 +2242,19 @@
         <v>200</v>
       </c>
       <c r="H41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
         <v>1800</v>
-      </c>
-      <c r="K41" s="3">
-        <v>4000</v>
-      </c>
-      <c r="L41" s="3">
-        <v>900</v>
       </c>
       <c r="M41" s="3">
         <v>4000</v>
@@ -2089,17 +2262,23 @@
       <c r="N41" s="3">
         <v>900</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
+      <c r="O41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="P41" s="3">
+        <v>900</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2116,13 +2295,13 @@
         <v>100</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2136,25 +2315,31 @@
       <c r="N42" s="3">
         <v>100</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>100</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
@@ -2172,7 +2357,7 @@
         <v>100</v>
       </c>
       <c r="K43" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="L43" s="3">
         <v>100</v>
@@ -2183,17 +2368,23 @@
       <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
+      <c r="O43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P43" s="3">
+        <v>100</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2230,25 +2421,31 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="E45" s="3">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="F45" s="3">
         <v>1200</v>
@@ -2257,19 +2454,19 @@
         <v>1200</v>
       </c>
       <c r="H45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J45" s="3">
         <v>2200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>300</v>
       </c>
       <c r="M45" s="3">
         <v>1000</v>
@@ -2277,25 +2474,31 @@
       <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
+      <c r="O45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P45" s="3">
+        <v>300</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1700</v>
+        <v>800</v>
       </c>
       <c r="E46" s="3">
-        <v>1700</v>
+        <v>800</v>
       </c>
       <c r="F46" s="3">
         <v>1700</v>
@@ -2304,19 +2507,19 @@
         <v>1700</v>
       </c>
       <c r="H46" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I46" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J46" s="3">
         <v>2700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4000</v>
-      </c>
-      <c r="K46" s="3">
-        <v>6200</v>
-      </c>
-      <c r="L46" s="3">
-        <v>1400</v>
       </c>
       <c r="M46" s="3">
         <v>6200</v>
@@ -2324,25 +2527,31 @@
       <c r="N46" s="3">
         <v>1400</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
+      <c r="O46" s="3">
+        <v>6200</v>
+      </c>
+      <c r="P46" s="3">
+        <v>1400</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3300</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -2371,46 +2580,52 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F48" s="3">
         <v>1000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1800</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1700</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1600</v>
       </c>
       <c r="M48" s="3">
         <v>1700</v>
@@ -2418,17 +2633,23 @@
       <c r="N48" s="3">
         <v>1600</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
+      <c r="O48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P48" s="3">
+        <v>1600</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2474,8 +2695,14 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2748,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,8 +2801,14 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2579,18 +2818,18 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2606,17 +2845,23 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,37 +2907,43 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F54" s="3">
         <v>2700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>4000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>4000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5800</v>
-      </c>
-      <c r="K54" s="3">
-        <v>7900</v>
-      </c>
-      <c r="L54" s="3">
-        <v>3000</v>
       </c>
       <c r="M54" s="3">
         <v>7900</v>
@@ -2700,17 +2951,23 @@
       <c r="N54" s="3">
         <v>3000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
+      <c r="O54" s="3">
+        <v>7900</v>
+      </c>
+      <c r="P54" s="3">
+        <v>3000</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2985,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,16 +3006,18 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="E57" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F57" s="3">
         <v>300</v>
@@ -2765,13 +3026,13 @@
         <v>300</v>
       </c>
       <c r="H57" s="3">
+        <v>300</v>
+      </c>
+      <c r="I57" s="3">
+        <v>300</v>
+      </c>
+      <c r="J57" s="3">
         <v>100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
@@ -2785,46 +3046,52 @@
       <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
+      <c r="O57" s="3">
+        <v>100</v>
+      </c>
+      <c r="P57" s="3">
+        <v>200</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
-      </c>
-      <c r="K58" s="3">
-        <v>500</v>
-      </c>
-      <c r="L58" s="3">
-        <v>900</v>
       </c>
       <c r="M58" s="3">
         <v>500</v>
@@ -2832,31 +3099,37 @@
       <c r="N58" s="3">
         <v>900</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
+      <c r="O58" s="3">
+        <v>500</v>
+      </c>
+      <c r="P58" s="3">
+        <v>900</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>700</v>
+        <v>2300</v>
       </c>
       <c r="E59" s="3">
-        <v>700</v>
+        <v>2300</v>
       </c>
       <c r="F59" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G59" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="H59" s="3">
         <v>500</v>
@@ -2865,13 +3138,13 @@
         <v>500</v>
       </c>
       <c r="J59" s="3">
+        <v>500</v>
+      </c>
+      <c r="K59" s="3">
+        <v>500</v>
+      </c>
+      <c r="L59" s="3">
         <v>1000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>8600</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1300</v>
       </c>
       <c r="M59" s="3">
         <v>8600</v>
@@ -2879,46 +3152,52 @@
       <c r="N59" s="3">
         <v>1300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
+      <c r="O59" s="3">
+        <v>8600</v>
+      </c>
+      <c r="P59" s="3">
+        <v>1300</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F60" s="3">
         <v>1600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2000</v>
-      </c>
-      <c r="K60" s="3">
-        <v>9500</v>
-      </c>
-      <c r="L60" s="3">
-        <v>2600</v>
       </c>
       <c r="M60" s="3">
         <v>9500</v>
@@ -2926,46 +3205,52 @@
       <c r="N60" s="3">
         <v>2600</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
+      <c r="O60" s="3">
+        <v>9500</v>
+      </c>
+      <c r="P60" s="3">
+        <v>2600</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F61" s="3">
         <v>6400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>6400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1400</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1600</v>
-      </c>
-      <c r="L61" s="3">
-        <v>1700</v>
       </c>
       <c r="M61" s="3">
         <v>1600</v>
@@ -2974,16 +3259,22 @@
         <v>1700</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2993,24 +3284,24 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>700</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3029,8 +3320,14 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3373,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3426,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,37 +3479,43 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F66" s="3">
         <v>8000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>8000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3400</v>
-      </c>
-      <c r="K66" s="3">
-        <v>11100</v>
-      </c>
-      <c r="L66" s="3">
-        <v>4300</v>
       </c>
       <c r="M66" s="3">
         <v>11100</v>
@@ -3208,17 +3523,23 @@
       <c r="N66" s="3">
         <v>4300</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
+      <c r="O66" s="3">
+        <v>11100</v>
+      </c>
+      <c r="P66" s="3">
+        <v>4300</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3557,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3606,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3659,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3712,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,37 +3765,43 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-25600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-25600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-14300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-14300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-8100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-8100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-6200</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-1300</v>
       </c>
       <c r="M72" s="3">
         <v>-3300</v>
@@ -3462,17 +3809,23 @@
       <c r="N72" s="3">
         <v>-1300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
+      <c r="O72" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="P72" s="3">
+        <v>-1300</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3871,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3924,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,37 +3977,43 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="F76" s="3">
         <v>-5400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-5400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2400</v>
-      </c>
-      <c r="K76" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="L76" s="3">
-        <v>-1300</v>
       </c>
       <c r="M76" s="3">
         <v>-3200</v>
@@ -3650,17 +4021,23 @@
       <c r="N76" s="3">
         <v>-1300</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
+      <c r="O76" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="P76" s="3">
+        <v>-1300</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,42 +4083,48 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
-      </c>
-      <c r="K80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="L80" s="2">
-        <v>44926</v>
       </c>
       <c r="M80" s="2">
         <v>45016</v>
@@ -3749,46 +4132,52 @@
       <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
+      <c r="O80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="P80" s="2">
+        <v>44926</v>
       </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-500</v>
       </c>
       <c r="M81" s="3">
         <v>-900</v>
@@ -3796,17 +4185,23 @@
       <c r="N81" s="3">
         <v>-500</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
+      <c r="O81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-500</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,37 +4219,39 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>100</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
-        <v>100</v>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
+        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -3862,8 +4259,8 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
@@ -3871,8 +4268,14 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4321,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4374,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4427,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4480,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,37 +4533,43 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1800</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1300</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-300</v>
       </c>
       <c r="M89" s="3">
         <v>-1200</v>
@@ -4144,17 +4577,23 @@
       <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
+      <c r="O89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="P89" s="3">
+        <v>-300</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4611,10 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4183,11 +4624,11 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -4219,8 +4660,14 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4713,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,8 +4766,14 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4324,11 +4783,11 @@
       <c r="E94" s="3">
         <v>0</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
@@ -4351,17 +4810,23 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4844,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4405,11 +4872,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>100</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4421,13 +4888,19 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4946,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4999,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,37 +5052,43 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F100" s="3">
         <v>2100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>2100</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I100" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
-      </c>
-      <c r="K100" s="3">
-        <v>2700</v>
-      </c>
-      <c r="L100" s="3">
-        <v>700</v>
       </c>
       <c r="M100" s="3">
         <v>2700</v>
@@ -4605,37 +5096,43 @@
       <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
+      <c r="O100" s="3">
+        <v>2700</v>
+      </c>
+      <c r="P100" s="3">
+        <v>700</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J101" s="3">
         <v>0</v>
@@ -4643,8 +5140,8 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4652,8 +5149,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
@@ -4661,8 +5158,14 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4679,19 +5182,19 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>100</v>
+      </c>
+      <c r="I102" s="3">
+        <v>100</v>
+      </c>
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1100</v>
-      </c>
-      <c r="K102" s="3">
-        <v>1500</v>
-      </c>
-      <c r="L102" s="3">
-        <v>400</v>
       </c>
       <c r="M102" s="3">
         <v>1500</v>
@@ -4699,13 +5202,19 @@
       <c r="N102" s="3">
         <v>400</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
+      <c r="O102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P102" s="3">
+        <v>400</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
